--- a/content/destination/downloads/travel-budget-template.xlsx
+++ b/content/destination/downloads/travel-budget-template.xlsx
@@ -543,6 +543,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Totals appear blank until you open this in Excel, Google Sheets or Numbers — they calculate on open.</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
